--- a/Template.xlsx
+++ b/Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\###PLN-W10 notebook\@Thammaratana\@load v1\run\test eff press v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B018F3-71F1-4F5C-8BBD-CCBAB6B086F4}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE71E6-6D16-42CB-BAEF-EB1C4EADC722}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Material</t>
   </si>
@@ -115,126 +115,6 @@
   </si>
   <si>
     <t>Goods receipt</t>
-  </si>
-  <si>
-    <t>4957737712</t>
-  </si>
-  <si>
-    <t>1/INM_34/A/3/20260803</t>
-  </si>
-  <si>
-    <t>4957741530</t>
-  </si>
-  <si>
-    <t>4957720261</t>
-  </si>
-  <si>
-    <t>4957724437</t>
-  </si>
-  <si>
-    <t>4957709210</t>
-  </si>
-  <si>
-    <t>12361-05010;A</t>
-  </si>
-  <si>
-    <t>312 Cap  4 Cyc (4x1) INJ  Rub</t>
-  </si>
-  <si>
-    <t>1/INJ_17/A/3/20260801</t>
-  </si>
-  <si>
-    <t>4957809142</t>
-  </si>
-  <si>
-    <t>4957788642</t>
-  </si>
-  <si>
-    <t>12361-35050;A</t>
-  </si>
-  <si>
-    <t>96 Cap  3 Cyc (2x1) 510  Rub</t>
-  </si>
-  <si>
-    <t>1/INM_29/A/2/20260720</t>
-  </si>
-  <si>
-    <t>4957720246</t>
-  </si>
-  <si>
-    <t>1/INM_29/A/3/20260720</t>
-  </si>
-  <si>
-    <t>4957716713</t>
-  </si>
-  <si>
-    <t>4957716644</t>
-  </si>
-  <si>
-    <t>4957694402</t>
-  </si>
-  <si>
-    <t>4957693980</t>
-  </si>
-  <si>
-    <t>4957693955</t>
-  </si>
-  <si>
-    <t>12771-09G00;A</t>
-  </si>
-  <si>
-    <t>1134 Cap  6 Cyc (8x1) 510  Rub</t>
-  </si>
-  <si>
-    <t>1/INM_38/E/3/20260717</t>
-  </si>
-  <si>
-    <t>4957873771</t>
-  </si>
-  <si>
-    <t>1/INM_38/E/3/20260807</t>
-  </si>
-  <si>
-    <t>4957830079</t>
-  </si>
-  <si>
-    <t>14566W000P;A</t>
-  </si>
-  <si>
-    <t>SEMI PART  2x1-COOL |8.0 cycle/hr</t>
-  </si>
-  <si>
-    <t>1/INJ_88/A/2/20260811</t>
-  </si>
-  <si>
-    <t>4957863521</t>
-  </si>
-  <si>
-    <t>1/INJ_88/A/3/20260811</t>
-  </si>
-  <si>
-    <t>4957867283</t>
-  </si>
-  <si>
-    <t>1/INJ_88/A/3/20260810</t>
-  </si>
-  <si>
-    <t>4957852748</t>
-  </si>
-  <si>
-    <t>4957853214</t>
-  </si>
-  <si>
-    <t>1/INJ_88/A/3/20260805</t>
-  </si>
-  <si>
-    <t>4957839416</t>
-  </si>
-  <si>
-    <t>1/INJ_88/A/2/20260805</t>
-  </si>
-  <si>
-    <t>4957835785</t>
   </si>
 </sst>
 </file>
@@ -1222,9 +1102,7 @@
       <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="4">
-        <v>3844.8</v>
-      </c>
+      <c r="I2" s="4"/>
       <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
@@ -1256,1180 +1134,466 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="3">
-        <v>312</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="4">
-        <v>6664.32</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="5">
-        <v>46239</v>
-      </c>
-      <c r="L3" s="5">
-        <v>46239</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0.82153935185185201</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="3">
-        <v>306</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="4">
-        <v>6536.16</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="5">
-        <v>46239</v>
-      </c>
-      <c r="L4" s="5">
-        <v>46240</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0.352835648148148</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T4" s="1"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="3">
-        <v>312</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="4">
-        <v>6664.32</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="5">
-        <v>46238</v>
-      </c>
-      <c r="L5" s="5">
-        <v>46238</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0.79578703703703701</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3">
-        <v>306</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="4">
-        <v>6536.16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="5">
-        <v>46238</v>
-      </c>
-      <c r="L6" s="5">
-        <v>46239</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0.32521990740740703</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3">
-        <v>222</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="4">
-        <v>4741.92</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="5">
-        <v>46237</v>
-      </c>
-      <c r="L7" s="5">
-        <v>46238</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0.31464120370370402</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="3">
-        <v>126</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="4">
-        <v>16514.82</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="5">
-        <v>46245</v>
-      </c>
-      <c r="L8" s="5">
-        <v>46247</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0.35825231481481501</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3">
-        <v>82</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="4">
-        <v>10747.74</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="5">
-        <v>46244</v>
-      </c>
-      <c r="L9" s="5">
-        <v>46245</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0.34225694444444399</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="3">
-        <v>30</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="4">
-        <v>4170.8999999999996</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="5">
-        <v>46238</v>
-      </c>
-      <c r="L10" s="5">
-        <v>46238</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0.79271990740740705</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="3">
-        <v>60</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="4">
-        <v>8341.7999999999993</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="5">
-        <v>46237</v>
-      </c>
-      <c r="L11" s="5">
-        <v>46238</v>
-      </c>
-      <c r="M11" s="6">
-        <v>0.62980324074074101</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="3">
-        <v>58</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="4">
-        <v>8063.74</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K12" s="5">
-        <v>46237</v>
-      </c>
-      <c r="L12" s="5">
-        <v>46238</v>
-      </c>
-      <c r="M12" s="6">
-        <v>0.62620370370370404</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="3">
-        <v>60</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="4">
-        <v>8341.7999999999993</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="5">
-        <v>46236</v>
-      </c>
-      <c r="L13" s="5">
-        <v>46237</v>
-      </c>
-      <c r="M13" s="6">
-        <v>0.32402777777777803</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="3">
-        <v>59</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="4">
-        <v>8202.77</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="5">
-        <v>46235</v>
-      </c>
-      <c r="L14" s="5">
-        <v>46236</v>
-      </c>
-      <c r="M14" s="6">
-        <v>0.78846064814814798</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="3">
-        <v>59</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="4">
-        <v>8202.77</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K15" s="5">
-        <v>46235</v>
-      </c>
-      <c r="L15" s="5">
-        <v>46236</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0.78050925925925896</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T15" s="1"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="3">
-        <v>36</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="4">
-        <v>808.56</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K16" s="5">
-        <v>46248</v>
-      </c>
-      <c r="L16" s="5">
-        <v>46252</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0.61344907407407401</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="3">
-        <v>170</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="4">
-        <v>3818.2</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" s="5">
-        <v>46247</v>
-      </c>
-      <c r="L17" s="5">
-        <v>46248</v>
-      </c>
-      <c r="M17" s="6">
-        <v>0.57903935185185196</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="3">
-        <v>100</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="4">
-        <v>24947</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="5">
-        <v>46251</v>
-      </c>
-      <c r="L18" s="5">
-        <v>46251</v>
-      </c>
-      <c r="M18" s="6">
-        <v>0.80923611111111104</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-      <c r="P18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="3">
-        <v>112</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I19" s="4">
-        <v>27940.639999999999</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" s="5">
-        <v>46251</v>
-      </c>
-      <c r="L19" s="5">
-        <v>46252</v>
-      </c>
-      <c r="M19" s="6">
-        <v>0.334895833333333</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-      <c r="P19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3">
-        <v>70</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="4">
-        <v>17462.900000000001</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" s="5">
-        <v>46249</v>
-      </c>
-      <c r="L20" s="5">
-        <v>46251</v>
-      </c>
-      <c r="M20" s="6">
-        <v>0.32347222222222199</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T20" s="1"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3">
-        <v>97</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="4">
-        <v>24198.59</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K21" s="5">
-        <v>46249</v>
-      </c>
-      <c r="L21" s="5">
-        <v>46251</v>
-      </c>
-      <c r="M21" s="6">
-        <v>0.35658564814814803</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T21" s="1"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" s="4">
-        <v>24947</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K22" s="5">
-        <v>46248</v>
-      </c>
-      <c r="L22" s="5">
-        <v>46249</v>
-      </c>
-      <c r="M22" s="6">
-        <v>0.31890046296296298</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T22" s="1"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="3">
-        <v>92</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="4">
-        <v>22951.24</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K23" s="5">
-        <v>46248</v>
-      </c>
-      <c r="L23" s="5">
-        <v>46248</v>
-      </c>
-      <c r="M23" s="6">
-        <v>0.81400462962963005</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="T23" s="1"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
